--- a/artfynd/A 49461-2024 artfynd.xlsx
+++ b/artfynd/A 49461-2024 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120740770</v>
+        <v>120740744</v>
       </c>
       <c r="B2" t="n">
-        <v>91083</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stor Sakriträsket, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748278</v>
+        <v>748090</v>
       </c>
       <c r="R2" t="n">
-        <v>7261550</v>
+        <v>7261782</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -774,44 +765,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mikael Hägg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120740771</v>
+        <v>120740745</v>
       </c>
       <c r="B3" t="n">
-        <v>91083</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748276</v>
+        <v>748129</v>
       </c>
       <c r="R3" t="n">
-        <v>7261553</v>
+        <v>7261773</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120740735</v>
+        <v>120740733</v>
       </c>
       <c r="B4" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748279</v>
+        <v>748317</v>
       </c>
       <c r="R4" t="n">
-        <v>7261567</v>
+        <v>7261554</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,22 +963,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hägg, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120740752</v>
+        <v>120740758</v>
       </c>
       <c r="B5" t="n">
-        <v>90705</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748268</v>
+        <v>748066</v>
       </c>
       <c r="R5" t="n">
-        <v>7261575</v>
+        <v>7261762</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120740753</v>
+        <v>120740760</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748066</v>
+        <v>748075</v>
       </c>
       <c r="R6" t="n">
-        <v>7261761</v>
+        <v>7261781</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,15 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120740768</v>
+        <v>120740761</v>
       </c>
       <c r="B7" t="n">
-        <v>82382</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,19 +1193,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stor Sakriträsket, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748264</v>
+        <v>748126</v>
       </c>
       <c r="R7" t="n">
-        <v>7261577</v>
+        <v>7261790</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1243,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1292,57 +1254,55 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120740729</v>
+        <v>120740767</v>
       </c>
       <c r="B8" t="n">
-        <v>90652</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stor Sakriträsket, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>748275</v>
+        <v>748298</v>
       </c>
       <c r="R8" t="n">
-        <v>7261618</v>
+        <v>7261550</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1343,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1394,57 +1355,55 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Hägg, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120740739</v>
+        <v>120740768</v>
       </c>
       <c r="B9" t="n">
-        <v>97025</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stor Sakriträsket, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>748189</v>
+        <v>748264</v>
       </c>
       <c r="R9" t="n">
-        <v>7261650</v>
+        <v>7261577</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1444,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1503,50 +1463,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120740740</v>
+        <v>120740769</v>
       </c>
       <c r="B10" t="n">
-        <v>97025</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stor Sakriträsket, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>748069</v>
+        <v>748254</v>
       </c>
       <c r="R10" t="n">
-        <v>7261778</v>
+        <v>7261589</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,6 +1545,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1605,15 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120740758</v>
+        <v>120784796</v>
       </c>
       <c r="B11" t="n">
-        <v>82382</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,16 +1593,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stor Sakriträsket, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>748066</v>
+        <v>748125</v>
       </c>
       <c r="R11" t="n">
-        <v>7261762</v>
+        <v>7261775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,33 +1646,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mikael Hägg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120740744</v>
+        <v>120784871</v>
       </c>
       <c r="B12" t="n">
-        <v>78680</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1723,34 +1676,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor Sakriträsket, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>748090</v>
+        <v>748245</v>
       </c>
       <c r="R12" t="n">
-        <v>7261782</v>
+        <v>7261625</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,55 +1747,51 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120740769</v>
+        <v>120740770</v>
       </c>
       <c r="B13" t="n">
-        <v>82382</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>4217</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>748254</v>
+        <v>748278</v>
       </c>
       <c r="R13" t="n">
-        <v>7261589</v>
+        <v>7261550</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,22 +1860,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120740741</v>
+        <v>120740771</v>
       </c>
       <c r="B14" t="n">
-        <v>97025</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1931,34 +1878,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor Sakriträsket, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>748286</v>
+        <v>748276</v>
       </c>
       <c r="R14" t="n">
-        <v>7261551</v>
+        <v>7261553</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,6 +1949,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2010,22 +1961,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120740751</v>
+        <v>120740736</v>
       </c>
       <c r="B15" t="n">
-        <v>90705</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,21 +1979,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>4745</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2057,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>748311</v>
+        <v>748225</v>
       </c>
       <c r="R15" t="n">
-        <v>7261563</v>
+        <v>7261653</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,60 +2058,52 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mikael Hägg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120740748</v>
+        <v>120740729</v>
       </c>
       <c r="B16" t="n">
-        <v>78680</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stor Sakriträsket, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>748301</v>
+        <v>748275</v>
       </c>
       <c r="R16" t="n">
-        <v>7261550</v>
+        <v>7261618</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,7 +2144,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2218,54 +2155,52 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120740738</v>
+        <v>120784136</v>
       </c>
       <c r="B17" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stor Sakriträsket, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>748275</v>
+        <v>748310</v>
       </c>
       <c r="R17" t="n">
         <v>7261575</v>
@@ -2309,55 +2244,51 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120740760</v>
+        <v>120740753</v>
       </c>
       <c r="B18" t="n">
-        <v>82382</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>748075</v>
+        <v>748066</v>
       </c>
       <c r="R18" t="n">
-        <v>7261781</v>
+        <v>7261761</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,50 +2360,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120740736</v>
+        <v>120784200</v>
       </c>
       <c r="B19" t="n">
-        <v>91589</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stor Sakriträsket, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>748225</v>
+        <v>748310</v>
       </c>
       <c r="R19" t="n">
-        <v>7261653</v>
+        <v>7261579</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,18 +2442,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2534,16 +2464,11 @@
         <v>120740737</v>
       </c>
       <c r="B20" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2626,44 +2551,39 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mikael Hägg, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120740733</v>
+        <v>120740738</v>
       </c>
       <c r="B21" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>748317</v>
+        <v>748275</v>
       </c>
       <c r="R21" t="n">
-        <v>7261554</v>
+        <v>7261575</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,22 +2648,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mikael Hägg, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120740767</v>
+        <v>120740735</v>
       </c>
       <c r="B22" t="n">
-        <v>82382</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2751,37 +2666,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stor Sakriträsket, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>748298</v>
+        <v>748279</v>
       </c>
       <c r="R22" t="n">
-        <v>7261550</v>
+        <v>7261567</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,7 +2734,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2834,60 +2745,52 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120784200</v>
+        <v>120740739</v>
       </c>
       <c r="B23" t="n">
-        <v>78598</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stor Sakriträsket, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>748310</v>
+        <v>748189</v>
       </c>
       <c r="R23" t="n">
-        <v>7261579</v>
+        <v>7261650</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,72 +2831,63 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120784871</v>
+        <v>120740740</v>
       </c>
       <c r="B24" t="n">
-        <v>82382</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stor Sakriträsket, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>748245</v>
+        <v>748069</v>
       </c>
       <c r="R24" t="n">
-        <v>7261625</v>
+        <v>7261778</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,34 +2928,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120784136</v>
+        <v>120740741</v>
       </c>
       <c r="B25" t="n">
-        <v>90652</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3069,37 +2957,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stor Sakriträsket, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>748310</v>
+        <v>748286</v>
       </c>
       <c r="R25" t="n">
-        <v>7261575</v>
+        <v>7261551</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3140,19 +3025,18 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 49461-2024 artfynd.xlsx
+++ b/artfynd/A 49461-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740744</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740745</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740733</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740758</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740760</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740761</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740767</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740768</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1561,6 +1606,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740769</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120784796</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1763,6 +1818,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120784871</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740770</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1965,6 +2030,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740771</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2062,6 +2132,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740736</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2159,6 +2234,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740729</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2260,6 +2340,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120784136</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2357,6 +2442,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740753</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2458,6 +2548,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120784200</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2555,6 +2650,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740737</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2652,6 +2752,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740738</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2749,6 +2854,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740735</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2846,6 +2956,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740739</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2943,6 +3058,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740740</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3040,8 +3160,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740741</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>